--- a/config/消防温感烟感.xlsx
+++ b/config/消防温感烟感.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="47">
   <si>
     <t>序号</t>
   </si>
@@ -87,7 +87,7 @@
     <t/>
   </si>
   <si>
-    <t>InputRegisters</t>
+    <t>HoldingRegisters</t>
   </si>
   <si>
     <t>AB</t>
@@ -136,9 +136,6 @@
   </si>
   <si>
     <t>修改modbus地址</t>
-  </si>
-  <si>
-    <t>HoldingRegisters</t>
   </si>
   <si>
     <t>modifyModbusAddress</t>
@@ -202,7 +199,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -655,19 +652,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -676,7 +673,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -808,7 +805,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1163,7 +1160,7 @@
     <col min="1" max="1" width="9" style="2"/>
     <col min="2" max="2" width="16.8174603174603" style="2" customWidth="1"/>
     <col min="3" max="6" width="9" style="2"/>
-    <col min="7" max="7" width="14.3888888888889" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.7222222222222" style="2" customWidth="1"/>
     <col min="8" max="12" width="9" style="2"/>
     <col min="13" max="13" width="21.9761904761905" style="2" customWidth="1"/>
     <col min="14" max="14" width="31.3412698412698" style="2" customWidth="1"/>
@@ -1171,52 +1168,52 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:16">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1239,7 +1236,7 @@
       <c r="F2" s="2">
         <v>19</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H2" s="2">
@@ -1289,7 +1286,7 @@
       <c r="F3" s="2">
         <v>20</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H3" s="2">
@@ -1339,7 +1336,7 @@
       <c r="F4" s="2">
         <v>21</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H4" s="2">
@@ -1389,7 +1386,7 @@
       <c r="F5" s="2">
         <v>22</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H5" s="2">
@@ -1439,7 +1436,7 @@
       <c r="F6" s="2">
         <v>23</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="2">
@@ -1485,7 +1482,7 @@
     <col min="1" max="1" width="9" style="2"/>
     <col min="2" max="2" width="16.8174603174603" style="2" customWidth="1"/>
     <col min="3" max="6" width="9" style="2"/>
-    <col min="7" max="7" width="14.3888888888889" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.7222222222222" style="2" customWidth="1"/>
     <col min="8" max="12" width="9" style="2"/>
     <col min="13" max="13" width="21.9761904761905" style="2" customWidth="1"/>
     <col min="14" max="14" width="31.3412698412698" style="2" customWidth="1"/>
@@ -1493,52 +1490,52 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:16">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1562,7 +1559,7 @@
         <v>14</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H2" s="2">
         <v>1</v>
@@ -1580,10 +1577,10 @@
         <v>18</v>
       </c>
       <c r="M2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>18</v>
@@ -1597,7 +1594,7 @@
         <v>2001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>17</v>
@@ -1612,7 +1609,7 @@
         <v>15</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H3" s="2">
         <v>1</v>
@@ -1630,10 +1627,10 @@
         <v>18</v>
       </c>
       <c r="M3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>18</v>
@@ -1647,7 +1644,7 @@
         <v>2002</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>
@@ -1662,7 +1659,7 @@
         <v>23</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H4" s="2">
         <v>1</v>
@@ -1680,10 +1677,10 @@
         <v>18</v>
       </c>
       <c r="M4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N4" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>18</v>
@@ -1697,7 +1694,7 @@
         <v>2003</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>17</v>
@@ -1712,7 +1709,7 @@
         <v>24</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H5" s="2">
         <v>1</v>
@@ -1730,10 +1727,10 @@
         <v>18</v>
       </c>
       <c r="M5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>18</v>

--- a/config/消防温感烟感.xlsx
+++ b/config/消防温感烟感.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18569" windowHeight="11268" activeTab="1"/>
+    <workbookView windowWidth="22010" windowHeight="12332"/>
   </bookViews>
   <sheets>
     <sheet name="遥测" sheetId="1" r:id="rId1"/>
@@ -1161,7 +1161,9 @@
     <col min="2" max="2" width="16.8174603174603" style="2" customWidth="1"/>
     <col min="3" max="6" width="9" style="2"/>
     <col min="7" max="7" width="16.7222222222222" style="2" customWidth="1"/>
-    <col min="8" max="12" width="9" style="2"/>
+    <col min="8" max="8" width="9" style="2"/>
+    <col min="9" max="9" width="13.2857142857143" style="2" customWidth="1"/>
+    <col min="10" max="12" width="9" style="2"/>
     <col min="13" max="13" width="21.9761904761905" style="2" customWidth="1"/>
     <col min="14" max="14" width="31.3412698412698" style="2" customWidth="1"/>
     <col min="15" max="16384" width="9" style="2"/>

--- a/config/消防温感烟感.xlsx
+++ b/config/消防温感烟感.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="47">
   <si>
     <t>序号</t>
   </si>
@@ -1453,8 +1453,8 @@
       <c r="K6" s="2">
         <v>0</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>18</v>
+      <c r="L6" s="2">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>33</v>
@@ -1575,8 +1575,8 @@
       <c r="K2" s="2">
         <v>0</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>18</v>
+      <c r="L2" s="2">
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>36</v>
@@ -1625,8 +1625,8 @@
       <c r="K3" s="2">
         <v>0</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>18</v>
+      <c r="L3" s="2">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>39</v>
@@ -1675,8 +1675,8 @@
       <c r="K4" s="2">
         <v>0</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>18</v>
+      <c r="L4" s="2">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>42</v>
@@ -1725,8 +1725,8 @@
       <c r="K5" s="2">
         <v>0</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>18</v>
+      <c r="L5" s="2">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>45</v>
